--- a/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -602,7 +602,7 @@
     <t>ImagingStudy.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -630,7 +630,7 @@
     <t>ImagingStudy.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -687,7 +687,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-servicerequest|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-careplan) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -719,7 +719,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitionerrole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -760,7 +760,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/endpoint-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -824,7 +824,7 @@
     <t>ImagingStudy.procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-procedure) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/procedure-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -933,7 +933,7 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-condition-problems-health-concerns|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-simple-observation|Media|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-diagnosticreport-note|DocumentReference) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/media-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1220,7 +1220,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1303,7 +1303,7 @@
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitionerrole|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-careteam|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-device|http://hl7.org/fhir/us/core/StructureDefinition/us-core-implantable-device|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-relatedperson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-relatedperson) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-imagingstudy-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
